--- a/ES_Semanal.xlsx
+++ b/ES_Semanal.xlsx
@@ -536,22 +536,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,16 +708,12 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -772,17 +768,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
@@ -832,11 +840,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -863,7 +867,11 @@
           <t>07:45</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>YOVANNA</t>
+        </is>
+      </c>
       <c r="C10" s="11" t="inlineStr"/>
       <c r="D10" s="11" t="inlineStr"/>
       <c r="E10" s="11" t="inlineStr"/>
@@ -890,11 +898,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="B11" s="10" t="inlineStr"/>
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
@@ -921,11 +925,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -952,7 +952,11 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>KEISY</t>
+        </is>
+      </c>
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="10" t="inlineStr"/>
@@ -1006,8 +1010,16 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
@@ -1033,11 +1045,7 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr"/>
       <c r="D16" s="11" t="inlineStr"/>
       <c r="E16" s="11" t="inlineStr"/>
@@ -1064,11 +1072,7 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="10" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>MIRLA</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr"/>
@@ -1128,15 +1132,19 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+          <t>ALDAID</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
+        </is>
+      </c>
       <c r="E19" s="10" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
@@ -1161,11 +1169,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
@@ -1177,11 +1181,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
@@ -1196,16 +1196,8 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr"/>
@@ -1231,16 +1223,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
@@ -1251,16 +1235,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
@@ -1274,13 +1250,21 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
       <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
@@ -1305,11 +1289,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
@@ -1321,11 +1301,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -1340,16 +1316,12 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr"/>
@@ -1360,8 +1332,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -1402,11 +1382,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="10" t="inlineStr"/>
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="10" t="inlineStr"/>
@@ -1418,11 +1394,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
@@ -1449,7 +1421,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>YOVANNA</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr"/>
@@ -1520,11 +1496,19 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr"/>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>DAYSI</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>ELVIS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SILVANA</t>
+        </is>
+      </c>
       <c r="E31" s="10" t="inlineStr"/>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr"/>
@@ -1536,7 +1520,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>YOVANNA</t>
+          <t>KEISY</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr"/>
@@ -1592,11 +1576,7 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
+      <c r="J33" s="10" t="inlineStr"/>
       <c r="K33" s="10" t="inlineStr"/>
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr"/>
@@ -1623,16 +1603,8 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
@@ -1648,14 +1620,34 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -1677,16 +1669,8 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr"/>
+      <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="11" t="inlineStr"/>
@@ -1699,14 +1683,10 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
+          <t>MIRLA</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr"/>
@@ -1720,11 +1700,7 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
       <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
@@ -1738,12 +1714,12 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
+          <t>ALDAID</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr"/>
@@ -1771,11 +1747,7 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr"/>
@@ -1790,16 +1762,8 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="B39" s="10" t="inlineStr"/>
+      <c r="C39" s="10" t="inlineStr"/>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr"/>
@@ -1810,11 +1774,7 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
@@ -1841,16 +1801,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr"/>
@@ -1864,16 +1816,8 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="inlineStr"/>
+      <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
       <c r="F41" s="10" t="inlineStr"/>
@@ -1886,12 +1830,24 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="10" t="inlineStr"/>
       <c r="P41" s="10" t="inlineStr"/>
@@ -1903,11 +1859,7 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="B42" s="11" t="inlineStr"/>
       <c r="C42" s="11" t="inlineStr"/>
       <c r="D42" s="11" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr"/>
@@ -1919,11 +1871,7 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr"/>
@@ -1938,8 +1886,16 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr"/>
-      <c r="C43" s="10" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>MERLY</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
+        </is>
+      </c>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr"/>
@@ -1950,10 +1906,26 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr"/>
@@ -1965,11 +1937,7 @@
           <t>16:15</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="B44" s="11" t="inlineStr"/>
       <c r="C44" s="11" t="inlineStr"/>
       <c r="D44" s="11" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr"/>
@@ -2052,12 +2020,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>MILAGROS</t>
+          <t>RENZO</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr"/>
@@ -2070,11 +2038,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
@@ -2091,7 +2055,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
+          <t>GIAN</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr"/>
@@ -2174,21 +2138,13 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr"/>
+      <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
@@ -2198,14 +2154,14 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr"/>
@@ -2223,24 +2179,20 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>PIERO</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>YENNIFER</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -2249,11 +2201,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
@@ -2268,10 +2216,26 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr"/>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
@@ -2280,11 +2244,7 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
@@ -2299,11 +2259,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
+      <c r="B54" s="11" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="11" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr"/>
@@ -2315,16 +2271,8 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr"/>
@@ -2338,16 +2286,8 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
       <c r="D55" s="10" t="inlineStr"/>
       <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
@@ -2358,7 +2298,11 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
@@ -2373,21 +2317,9 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
@@ -2397,21 +2329,9 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
       <c r="O56" s="11" t="inlineStr"/>
@@ -2436,11 +2356,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="J57" s="10" t="inlineStr"/>
       <c r="K57" s="10" t="inlineStr"/>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr"/>
@@ -2494,11 +2410,7 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="J59" s="10" t="inlineStr"/>
       <c r="K59" s="10" t="inlineStr"/>
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
@@ -2552,8 +2464,16 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>MERLY</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
+        </is>
+      </c>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
       <c r="N61" s="10" t="inlineStr"/>
@@ -2579,11 +2499,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
@@ -2610,11 +2526,7 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
+      <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="10" t="inlineStr"/>
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="inlineStr"/>
@@ -2668,8 +2580,16 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>AXEL</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>RENZO</t>
+        </is>
+      </c>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
       <c r="N65" s="10" t="inlineStr"/>
@@ -2697,19 +2617,11 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
+          <t>GIAN</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
       <c r="O66" s="11" t="inlineStr"/>
@@ -2736,34 +2648,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>ELVIS</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
       <c r="Q67" s="10" t="inlineStr"/>
     </row>
@@ -2812,9 +2712,9 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr"/>
@@ -2845,15 +2745,19 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>JHOSSEPI</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="L70" s="11" t="inlineStr"/>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
@@ -2880,28 +2784,44 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>JEFFERSON</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>ANDRE</t>
+          <t>MAFER</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -3006,22 +2926,22 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3182,10 +3102,14 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -3242,20 +3166,24 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>EMIR</t>
+          <t>MANUEL</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>MIRLA</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
+          <t>PILAR</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
@@ -3308,11 +3236,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -3340,7 +3264,11 @@
           <t>07:45</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
       <c r="C10" s="11" t="inlineStr"/>
       <c r="D10" s="11" t="inlineStr"/>
       <c r="E10" s="11" t="inlineStr"/>
@@ -3368,11 +3296,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="B11" s="10" t="inlineStr"/>
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
@@ -3400,11 +3324,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -3490,7 +3410,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ENZO</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
@@ -3550,11 +3470,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>DAYSI</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr"/>
@@ -3608,13 +3536,17 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>KEISY</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="10" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
@@ -3640,11 +3572,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
@@ -3674,7 +3602,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CYNTHIA</t>
+          <t>ALDAID</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr"/>
@@ -3704,16 +3632,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
@@ -3724,21 +3644,9 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
       <c r="O22" s="11" t="inlineStr"/>
@@ -3752,14 +3660,14 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -3788,16 +3696,8 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
@@ -3808,11 +3708,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -3830,14 +3726,10 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr"/>
@@ -3848,8 +3740,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>MIRLA</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -3864,11 +3764,7 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
+      <c r="B26" s="11" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr"/>
       <c r="D26" s="11" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr"/>
@@ -3908,11 +3804,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
@@ -3928,7 +3820,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>SILVANA</t>
+        </is>
+      </c>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr"/>
@@ -3940,7 +3836,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr"/>
@@ -3996,11 +3896,7 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="11" t="inlineStr"/>
@@ -4100,7 +3996,11 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>KATHERIN</t>
+        </is>
+      </c>
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="11" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr"/>
@@ -4112,11 +4012,7 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
@@ -4132,31 +4028,43 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -4184,11 +4092,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr"/>
@@ -4204,16 +4108,8 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr"/>
@@ -4226,15 +4122,15 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>MIRLA</t>
+          <t>KEISY</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr"/>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
       <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" s="10" t="inlineStr"/>
@@ -4248,11 +4144,7 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
+      <c r="B38" s="11" t="inlineStr"/>
       <c r="C38" s="11" t="inlineStr"/>
       <c r="D38" s="11" t="inlineStr"/>
       <c r="E38" s="11" t="inlineStr"/>
@@ -4264,16 +4156,8 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr"/>
       <c r="N38" s="11" t="inlineStr"/>
@@ -4300,9 +4184,9 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>ALDAID</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr"/>
@@ -4320,16 +4204,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr"/>
@@ -4340,16 +4216,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr"/>
@@ -4366,14 +4234,10 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
+          <t>GIAN</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
       <c r="F41" s="10" t="inlineStr"/>
@@ -4384,18 +4248,26 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="10" t="inlineStr"/>
       <c r="P41" s="10" t="inlineStr"/>
@@ -4436,7 +4308,11 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="C43" s="10" t="inlineStr"/>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="inlineStr"/>
@@ -4448,9 +4324,21 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
       <c r="M43" s="10" t="inlineStr"/>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
@@ -4550,14 +4438,10 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+          <t>AXEL</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr"/>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="10" t="inlineStr"/>
       <c r="F47" s="10" t="inlineStr"/>
@@ -4568,11 +4452,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
@@ -4616,7 +4496,11 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
       <c r="C49" s="10" t="inlineStr"/>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr"/>
@@ -4644,7 +4528,11 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>GREYS</t>
+        </is>
+      </c>
       <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="11" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr"/>
@@ -4656,11 +4544,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="11" t="inlineStr"/>
@@ -4678,15 +4562,19 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr"/>
+          <t>SALOME</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
@@ -4696,7 +4584,11 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
       <c r="M51" s="10" t="inlineStr"/>
@@ -4714,24 +4606,16 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -4740,16 +4624,8 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
@@ -4764,14 +4640,26 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
@@ -4782,15 +4670,19 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
-      <c r="L53" s="10" t="inlineStr"/>
+          <t>DAYSI</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="M53" s="10" t="inlineStr"/>
       <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
@@ -4832,26 +4724,10 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
@@ -4860,16 +4736,8 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
       <c r="N55" s="10" t="inlineStr"/>
@@ -4884,21 +4752,9 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
@@ -4908,16 +4764,8 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
@@ -5000,7 +4848,11 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>GIAN</t>
+        </is>
+      </c>
       <c r="K59" s="10" t="inlineStr"/>
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
@@ -5028,11 +4880,7 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr"/>
@@ -5060,7 +4908,11 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="K61" s="10" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
@@ -5088,16 +4940,8 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr"/>
@@ -5152,7 +4996,11 @@
           <t>21:15</t>
         </is>
       </c>
-      <c r="J64" s="11" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>SILVANA</t>
+        </is>
+      </c>
       <c r="K64" s="11" t="inlineStr"/>
       <c r="L64" s="11" t="inlineStr"/>
       <c r="M64" s="11" t="inlineStr"/>
@@ -5180,7 +5028,11 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>AXEL</t>
+        </is>
+      </c>
       <c r="K65" s="10" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
@@ -5208,16 +5060,8 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
@@ -5246,24 +5090,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
       <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
@@ -5290,7 +5122,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>JULISSA</t>
+          <t>GREYS</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -5320,9 +5152,21 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
       <c r="M69" s="10" t="inlineStr"/>
       <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr"/>
@@ -5350,24 +5194,20 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>JHOSSEPI</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
       <c r="P70" s="11" t="inlineStr"/>
@@ -5394,29 +5234,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>ROSARIOC</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -5524,10 +5384,10 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
@@ -5535,11 +5395,11 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5698,16 +5558,12 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -5764,17 +5620,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
+          <t>KIOMI</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
@@ -5826,11 +5694,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -5888,7 +5752,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr"/>
@@ -5918,11 +5782,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -6006,7 +5866,11 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
       <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
@@ -6034,11 +5898,7 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr"/>
       <c r="D16" s="11" t="inlineStr"/>
       <c r="E16" s="11" t="inlineStr"/>
@@ -6066,8 +5926,16 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="10" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
@@ -6124,22 +5992,22 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>LILIA</t>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>JoseLuis</t>
+          <t>JOSELUIS</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
@@ -6166,11 +6034,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
@@ -6182,11 +6046,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
@@ -6204,10 +6064,14 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr"/>
+          <t>KEISY</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>YOVANNA</t>
+        </is>
+      </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr"/>
@@ -6234,16 +6098,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
@@ -6254,16 +6110,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
@@ -6278,12 +6126,16 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr"/>
@@ -6310,16 +6162,8 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
@@ -6330,11 +6174,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -6350,11 +6190,7 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
@@ -6366,8 +6202,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>KIOMI</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -6382,11 +6226,7 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="B26" s="11" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr"/>
       <c r="D26" s="11" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr"/>
@@ -6398,11 +6238,7 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
+      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr"/>
@@ -6430,11 +6266,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
@@ -6490,7 +6322,11 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
       <c r="K29" s="10" t="inlineStr"/>
       <c r="L29" s="10" t="inlineStr"/>
       <c r="M29" s="10" t="inlineStr"/>
@@ -6590,7 +6426,11 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>DAYSI</t>
+        </is>
+      </c>
       <c r="C33" s="10" t="inlineStr"/>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr"/>
@@ -6620,7 +6460,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
@@ -6634,21 +6474,9 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
       <c r="O34" s="11" t="inlineStr"/>
@@ -6664,29 +6492,41 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>YASMIN</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -6702,11 +6542,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr"/>
@@ -6718,11 +6554,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr"/>
@@ -6738,16 +6570,8 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr"/>
@@ -6760,15 +6584,19 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr"/>
+          <t>KATHERINE</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
       <c r="M37" s="10" t="inlineStr"/>
       <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" s="10" t="inlineStr"/>
@@ -6794,11 +6622,7 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr"/>
@@ -6814,11 +6638,7 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="B39" s="10" t="inlineStr"/>
       <c r="C39" s="10" t="inlineStr"/>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="inlineStr"/>
@@ -6830,12 +6650,16 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>KEISY</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>YOVANNA</t>
+        </is>
+      </c>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
       <c r="N39" s="10" t="inlineStr"/>
@@ -6862,11 +6686,7 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
@@ -6882,16 +6702,8 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="inlineStr"/>
+      <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
       <c r="F41" s="10" t="inlineStr"/>
@@ -6902,17 +6714,21 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr"/>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="M41" s="10" t="inlineStr"/>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="10" t="inlineStr"/>
@@ -6956,7 +6772,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MIRIANM</t>
+          <t>RENZO</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr"/>
@@ -6970,9 +6786,21 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="M43" s="10" t="inlineStr"/>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
@@ -7070,11 +6898,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+      <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="10" t="inlineStr"/>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="10" t="inlineStr"/>
@@ -7130,8 +6954,16 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
-      <c r="C49" s="10" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>GIAN</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>GREYS</t>
+        </is>
+      </c>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr"/>
@@ -7158,11 +6990,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+      <c r="B50" s="11" t="inlineStr"/>
       <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="11" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr"/>
@@ -7174,11 +7002,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="11" t="inlineStr"/>
@@ -7196,11 +7020,19 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr"/>
-      <c r="D51" s="10" t="inlineStr"/>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
@@ -7212,7 +7044,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
@@ -7232,24 +7064,16 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -7258,21 +7082,9 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
       <c r="O52" s="11" t="inlineStr"/>
@@ -7286,15 +7098,31 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
       <c r="I53" s="10" t="inlineStr">
@@ -7302,9 +7130,21 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="M53" s="10" t="inlineStr"/>
       <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
@@ -7318,11 +7158,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
+      <c r="B54" s="11" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="11" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr"/>
@@ -7334,11 +7170,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr"/>
@@ -7354,21 +7186,9 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
       <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
@@ -7380,7 +7200,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>LILIA</t>
+          <t>SILVANA</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr"/>
@@ -7398,11 +7218,7 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
       <c r="C56" s="11" t="inlineStr"/>
       <c r="D56" s="11" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr"/>
@@ -7414,16 +7230,8 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
@@ -7478,11 +7286,7 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr"/>
@@ -7538,11 +7342,7 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr"/>
@@ -7570,7 +7370,11 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>RENZO</t>
+        </is>
+      </c>
       <c r="K61" s="10" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
@@ -7598,11 +7402,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
@@ -7686,11 +7486,7 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+      <c r="J65" s="10" t="inlineStr"/>
       <c r="K65" s="10" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
@@ -7718,11 +7514,7 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
+      <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
@@ -7752,24 +7544,16 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
+          <t>GIAN</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>GREYS</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
       <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
@@ -7794,11 +7578,7 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="J68" s="11" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr"/>
       <c r="L68" s="11" t="inlineStr"/>
       <c r="M68" s="11" t="inlineStr"/>
@@ -7828,12 +7608,24 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
+          <t>DAYSI</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr"/>
       <c r="P69" s="10" t="inlineStr"/>
@@ -7860,24 +7652,20 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>JHOSSEPI</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
       <c r="P70" s="11" t="inlineStr"/>
@@ -7904,21 +7692,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -8025,23 +7841,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8200,16 +8016,12 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -8266,17 +8078,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MIRLA</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
@@ -8328,11 +8152,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -8360,7 +8180,11 @@
           <t>07:45</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KIOMI</t>
+        </is>
+      </c>
       <c r="C10" s="11" t="inlineStr"/>
       <c r="D10" s="11" t="inlineStr"/>
       <c r="E10" s="11" t="inlineStr"/>
@@ -8388,11 +8212,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="B11" s="10" t="inlineStr"/>
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
@@ -8420,11 +8240,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -8508,9 +8324,21 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr"/>
@@ -8564,11 +8392,7 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="10" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
@@ -8596,7 +8420,11 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>YOVANNA</t>
+        </is>
+      </c>
       <c r="C18" s="11" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -8626,20 +8454,20 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>KEISYS</t>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>MIRLA</t>
+          <t>SILVANA</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr"/>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr"/>
@@ -8664,11 +8492,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
@@ -8680,11 +8504,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
@@ -8700,11 +8520,7 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="10" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
@@ -8732,21 +8548,9 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
+      <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
       <c r="G22" s="11" t="inlineStr"/>
@@ -8756,16 +8560,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
@@ -8780,8 +8576,16 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="10" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr"/>
@@ -8808,21 +8612,9 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr"/>
+      <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
@@ -8832,11 +8624,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -8852,9 +8640,9 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr"/>
@@ -8868,8 +8656,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>MIRLA</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -8924,11 +8720,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
@@ -8956,7 +8748,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>KIOMI</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr"/>
@@ -9030,7 +8826,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr"/>
@@ -9118,7 +8914,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
@@ -9132,21 +8928,9 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
       <c r="O34" s="11" t="inlineStr"/>
@@ -9162,25 +8946,41 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -9196,11 +8996,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr"/>
@@ -9214,7 +9010,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>CYNTHIA</t>
+          <t>YOVANNA</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -9232,16 +9028,8 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr"/>
@@ -9254,19 +9042,15 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>KATHERINE</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
       <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" s="10" t="inlineStr"/>
@@ -9320,16 +9104,8 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
       <c r="N39" s="10" t="inlineStr"/>
@@ -9344,11 +9120,7 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
       <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr"/>
@@ -9360,11 +9132,7 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
@@ -9380,11 +9148,7 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="inlineStr"/>
       <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
@@ -9398,11 +9162,19 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="M41" s="10" t="inlineStr"/>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="10" t="inlineStr"/>
@@ -9416,7 +9188,11 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="C42" s="11" t="inlineStr"/>
       <c r="D42" s="11" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr"/>
@@ -9444,11 +9220,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="B43" s="10" t="inlineStr"/>
       <c r="C43" s="10" t="inlineStr"/>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="inlineStr"/>
@@ -9460,10 +9232,26 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr"/>
@@ -9532,11 +9320,7 @@
           <t>16:45</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="B46" s="11" t="inlineStr"/>
       <c r="C46" s="11" t="inlineStr"/>
       <c r="D46" s="11" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr"/>
@@ -9548,11 +9332,7 @@
           <t>16:45</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
       <c r="M46" s="11" t="inlineStr"/>
@@ -9570,7 +9350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr"/>
@@ -9584,11 +9364,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
@@ -9632,7 +9408,11 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="C49" s="10" t="inlineStr"/>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr"/>
@@ -9660,16 +9440,8 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
+      <c r="B50" s="11" t="inlineStr"/>
+      <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="11" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr"/>
       <c r="F50" s="11" t="inlineStr"/>
@@ -9696,9 +9468,9 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr"/>
@@ -9714,11 +9486,19 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr"/>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="M51" s="10" t="inlineStr"/>
       <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" s="10" t="inlineStr"/>
@@ -9734,24 +9514,20 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>BRYANR</t>
+          <t>GREYS</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>RAUL</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
+          <t>SALOME</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -9760,16 +9536,8 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
@@ -9784,14 +9552,26 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
@@ -9800,11 +9580,7 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
@@ -9848,21 +9624,9 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
       <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
@@ -9874,7 +9638,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>SILVANA</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr"/>
@@ -9892,21 +9656,9 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
@@ -9916,11 +9668,7 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
@@ -9976,11 +9724,7 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr"/>
@@ -10036,9 +9780,9 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -10068,11 +9812,7 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="J61" s="10" t="inlineStr"/>
       <c r="K61" s="10" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
@@ -10100,11 +9840,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
@@ -10190,14 +9926,10 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
+          <t>AXEL</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
       <c r="N65" s="10" t="inlineStr"/>
@@ -10224,11 +9956,7 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
+      <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
@@ -10258,24 +9986,16 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>BRYANR</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
       <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
@@ -10300,11 +10020,7 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
+      <c r="J68" s="11" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr"/>
       <c r="L68" s="11" t="inlineStr"/>
       <c r="M68" s="11" t="inlineStr"/>
@@ -10332,7 +10048,11 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="K69" s="10" t="inlineStr"/>
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="inlineStr"/>
@@ -10362,22 +10082,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>JHOSSEPI</t>
+          <t>GREYS</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>LINDSAYF</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
+          <t>MERLY</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="N70" s="11" t="inlineStr"/>
@@ -10406,29 +10126,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>CRISTOPHERY</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>ERIKAO</t>
+          <t>LIZBET</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
+          <t>MAFER</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -10535,23 +10275,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10712,10 +10452,14 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -10772,21 +10516,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ENZO</t>
+          <t>ESTRELLA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>LIZ</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
@@ -10838,11 +10590,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -10872,7 +10620,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr"/>
@@ -10930,11 +10678,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -11018,7 +10762,11 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
       <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
@@ -11046,11 +10794,7 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr"/>
       <c r="D16" s="11" t="inlineStr"/>
       <c r="E16" s="11" t="inlineStr"/>
@@ -11078,9 +10822,21 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="10" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ELVIS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr"/>
@@ -11106,11 +10862,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -11140,17 +10892,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
+          <t>DIEGO</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>JoseLuis</t>
+          <t>ANDRE</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
@@ -11178,9 +10930,9 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr"/>
@@ -11210,11 +10962,7 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="10" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
@@ -11242,21 +10990,9 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
+      <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
       <c r="G22" s="11" t="inlineStr"/>
@@ -11266,21 +11002,9 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
       <c r="O22" s="11" t="inlineStr"/>
@@ -11294,11 +11018,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
+      <c r="B23" s="4" t="inlineStr"/>
       <c r="C23" s="10" t="inlineStr"/>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr"/>
@@ -11326,16 +11046,12 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
@@ -11346,11 +11062,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -11366,21 +11078,13 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr"/>
@@ -11392,10 +11096,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -11450,11 +11158,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
@@ -11470,7 +11174,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>FLOR</t>
+        </is>
+      </c>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr"/>
@@ -11482,7 +11190,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr"/>
@@ -11498,7 +11210,11 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="inlineStr"/>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="10" t="inlineStr"/>
@@ -11554,7 +11270,11 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
       <c r="C31" s="10" t="inlineStr"/>
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr"/>
@@ -11566,11 +11286,7 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="J31" s="10" t="inlineStr"/>
       <c r="K31" s="10" t="inlineStr"/>
       <c r="L31" s="10" t="inlineStr"/>
       <c r="M31" s="10" t="inlineStr"/>
@@ -11626,11 +11342,7 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
+      <c r="J33" s="10" t="inlineStr"/>
       <c r="K33" s="10" t="inlineStr"/>
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr"/>
@@ -11648,7 +11360,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
@@ -11662,11 +11374,7 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
@@ -11684,13 +11392,29 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
@@ -11698,7 +11422,11 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>DIEGO</t>
+        </is>
+      </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -11714,11 +11442,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr"/>
@@ -11730,11 +11454,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr"/>
@@ -11750,16 +11470,8 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr"/>
@@ -11770,14 +11482,14 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr"/>
@@ -11808,7 +11520,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>BRINDY</t>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -11838,11 +11550,7 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+      <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
@@ -11858,16 +11566,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr"/>
@@ -11878,21 +11578,9 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr"/>
       <c r="O40" s="11" t="inlineStr"/>
@@ -11906,11 +11594,7 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="inlineStr"/>
       <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
@@ -11922,13 +11606,17 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="M41" s="10" t="inlineStr"/>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="10" t="inlineStr"/>
@@ -11982,10 +11670,26 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>ESTRELLA</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>LIZ</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr"/>
@@ -12026,11 +11730,7 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+      <c r="B45" s="10" t="inlineStr"/>
       <c r="C45" s="10" t="inlineStr"/>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="10" t="inlineStr"/>
@@ -12086,11 +11786,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="10" t="inlineStr"/>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="10" t="inlineStr"/>
@@ -12204,15 +11900,19 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>GREYS</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr"/>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
@@ -12224,7 +11924,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>YASMIN</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
@@ -12244,17 +11944,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
+          <t>DANA</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
+          <t>KIOMI</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr"/>
@@ -12266,16 +11966,8 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
@@ -12292,13 +11984,29 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr"/>
+          <t>VENUS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
       <c r="I53" s="10" t="inlineStr">
@@ -12306,9 +12014,21 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>ELVIS</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="M53" s="10" t="inlineStr"/>
       <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
@@ -12322,11 +12042,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
+      <c r="B54" s="11" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="11" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr"/>
@@ -12338,11 +12054,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr"/>
@@ -12358,26 +12070,10 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
@@ -12386,21 +12082,9 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
       <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" s="10" t="inlineStr"/>
@@ -12414,26 +12098,10 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
       <c r="H56" s="11" t="inlineStr"/>
@@ -12442,16 +12110,8 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
@@ -12506,11 +12166,7 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr"/>
@@ -12568,14 +12224,10 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>RAUL</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr"/>
@@ -12630,11 +12282,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
@@ -12662,7 +12310,11 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>FLOR</t>
+        </is>
+      </c>
       <c r="K63" s="10" t="inlineStr"/>
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="inlineStr"/>
@@ -12718,7 +12370,11 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
+        </is>
+      </c>
       <c r="K65" s="10" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
@@ -12746,16 +12402,8 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>ELIZABETH</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>YASSER</t>
-        </is>
-      </c>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
@@ -12784,24 +12432,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
       <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
@@ -12826,7 +12462,11 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="J68" s="11" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>VENUS</t>
+        </is>
+      </c>
       <c r="K68" s="11" t="inlineStr"/>
       <c r="L68" s="11" t="inlineStr"/>
       <c r="M68" s="11" t="inlineStr"/>
@@ -12856,11 +12496,19 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
+          <t>GREYS</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="M69" s="10" t="inlineStr"/>
       <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr"/>
@@ -12888,29 +12536,25 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LINDSAYF</t>
+          <t>DANA</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>MAFER</t>
+          <t>KIOMI</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
       <c r="P70" s="11" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr"/>
@@ -12936,33 +12580,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>CRISTOPHERY</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>JEFFERSON</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>ROSARIOC</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -13069,23 +12729,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13244,16 +12904,12 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
@@ -13310,18 +12966,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -13372,9 +13044,9 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr"/>
@@ -13406,7 +13078,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>MIRLA</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr"/>
@@ -13436,11 +13108,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="B11" s="10" t="inlineStr"/>
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
@@ -13524,11 +13192,7 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
+      <c r="B14" s="11" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr"/>
       <c r="D14" s="11" t="inlineStr"/>
       <c r="E14" s="11" t="inlineStr"/>
@@ -13558,7 +13222,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t>KEISY</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
@@ -13588,7 +13252,11 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>KATHERIN</t>
+        </is>
+      </c>
       <c r="C16" s="11" t="inlineStr"/>
       <c r="D16" s="11" t="inlineStr"/>
       <c r="E16" s="11" t="inlineStr"/>
@@ -13618,10 +13286,14 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
+          <t>MIRLA</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
@@ -13648,11 +13320,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -13682,20 +13350,24 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr"/>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr"/>
@@ -13720,16 +13392,8 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
       <c r="F20" s="11" t="inlineStr"/>
@@ -13740,11 +13404,7 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
@@ -13762,10 +13422,14 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr"/>
+          <t>ALDAID</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>VENUS</t>
+        </is>
+      </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr"/>
@@ -13792,11 +13456,7 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
@@ -13808,11 +13468,7 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
       <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
@@ -13830,17 +13486,25 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ELIZABETH</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr"/>
-      <c r="F23" s="10" t="inlineStr"/>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr"/>
       <c r="I23" s="10" t="inlineStr">
@@ -13864,21 +13528,9 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr"/>
+      <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
@@ -13888,11 +13540,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -13908,11 +13556,7 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
+      <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
@@ -13924,12 +13568,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>MIRLA</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -13956,11 +13604,7 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr"/>
@@ -13976,11 +13620,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="10" t="inlineStr"/>
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="10" t="inlineStr"/>
@@ -14020,7 +13660,11 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr"/>
@@ -14036,7 +13680,11 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="inlineStr"/>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="10" t="inlineStr"/>
@@ -14064,7 +13712,11 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>DAYSI</t>
+        </is>
+      </c>
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="11" t="inlineStr"/>
       <c r="E30" s="11" t="inlineStr"/>
@@ -14092,11 +13744,7 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
+      <c r="B31" s="10" t="inlineStr"/>
       <c r="C31" s="10" t="inlineStr"/>
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr"/>
@@ -14136,11 +13784,7 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr"/>
@@ -14156,11 +13800,7 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
+      <c r="B33" s="10" t="inlineStr"/>
       <c r="C33" s="10" t="inlineStr"/>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr"/>
@@ -14174,7 +13814,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
+          <t>KEISY</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr"/>
@@ -14204,16 +13844,8 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>JoseLuis</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
@@ -14233,9 +13865,21 @@
           <t>LIZBET</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
@@ -14244,7 +13888,11 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>MIRLA</t>
+        </is>
+      </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -14272,11 +13920,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>CYNTHIA</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr"/>
@@ -14292,11 +13936,7 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
       <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
@@ -14308,12 +13948,16 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>JOSELUIS</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
+        </is>
+      </c>
       <c r="L37" s="10" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
       <c r="N37" s="10" t="inlineStr"/>
@@ -14340,11 +13984,7 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr"/>
@@ -14360,7 +14000,11 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="C39" s="10" t="inlineStr"/>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="inlineStr"/>
@@ -14374,14 +14018,10 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+          <t>ALDAID</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
       <c r="N39" s="10" t="inlineStr"/>
@@ -14396,16 +14036,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr"/>
@@ -14416,11 +14048,7 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr"/>
@@ -14436,9 +14064,9 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>GIAN</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr"/>
@@ -14452,16 +14080,32 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" s="10" t="inlineStr"/>
-      <c r="O41" s="10" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="P41" s="10" t="inlineStr"/>
       <c r="Q41" s="10" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
@@ -14474,7 +14118,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>BRYANR</t>
+          <t>FLOR</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr"/>
@@ -14488,16 +14132,8 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr"/>
@@ -14524,10 +14160,26 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr"/>
@@ -14540,7 +14192,11 @@
           <t>16:15</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="C44" s="11" t="inlineStr"/>
       <c r="D44" s="11" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr"/>
@@ -14580,7 +14236,11 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
       <c r="M45" s="10" t="inlineStr"/>
@@ -14654,7 +14314,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
+          <t>RENZO</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr"/>
@@ -14668,11 +14328,7 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="11" t="inlineStr"/>
@@ -14688,7 +14344,11 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>KIOMI</t>
+        </is>
+      </c>
       <c r="C49" s="10" t="inlineStr"/>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr"/>
@@ -14716,11 +14376,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="B50" s="11" t="inlineStr"/>
       <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="11" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr"/>
@@ -14732,11 +14388,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="11" t="inlineStr"/>
@@ -14752,16 +14404,12 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>JOSELYN</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr"/>
       <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
@@ -14772,11 +14420,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>ROCIO</t>
-        </is>
-      </c>
+      <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
       <c r="M51" s="10" t="inlineStr"/>
@@ -14794,20 +14438,24 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr"/>
+          <t>MERLY</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>PIERO</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -14816,9 +14464,9 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
@@ -14836,11 +14484,31 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr"/>
-      <c r="C53" s="10" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
       <c r="I53" s="10" t="inlineStr">
@@ -14848,7 +14516,11 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
@@ -14864,11 +14536,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
+      <c r="B54" s="11" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="11" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr"/>
@@ -14896,31 +14564,11 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
       <c r="I55" s="10" t="inlineStr">
@@ -14930,19 +14578,15 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+          <t>SILVANA</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
       <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" s="10" t="inlineStr"/>
@@ -14956,21 +14600,9 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
@@ -14982,19 +14614,11 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+          <t>VENUS</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
       <c r="O56" s="11" t="inlineStr"/>
@@ -15020,9 +14644,9 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr"/>
@@ -15052,11 +14676,7 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>ELIZABETH</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr"/>
@@ -15084,7 +14704,11 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>GIAN</t>
+        </is>
+      </c>
       <c r="K59" s="10" t="inlineStr"/>
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
@@ -15112,11 +14736,7 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr"/>
@@ -15172,7 +14792,11 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr"/>
@@ -15200,11 +14824,7 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
+      <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="10" t="inlineStr"/>
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="inlineStr"/>
@@ -15260,9 +14880,9 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr"/>
@@ -15294,12 +14914,12 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>JOSELYN</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>RENZO</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr"/>
@@ -15330,24 +14950,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
+          <t>KIOMI</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
       <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr"/>
@@ -15402,10 +15010,14 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr"/>
+          <t>FLOR</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="inlineStr"/>
       <c r="N69" s="10" t="inlineStr"/>
@@ -15434,29 +15046,25 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>JHOSSEPI</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>PIERO</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
       <c r="P70" s="11" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr"/>
@@ -15482,29 +15090,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>CRISTOPHERY</t>
+          <t>LIZBET</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>LIZBET</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>ROSARIOC</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>CYNTHIA</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -15611,23 +15239,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15786,14 +15414,14 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ESTRELLA</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
@@ -15852,18 +15480,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
+          <t>ESTRELLA</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>LIZ</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -15916,10 +15560,14 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr"/>
+          <t>MIGUEL</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
       <c r="F9" s="10" t="inlineStr"/>
@@ -15974,9 +15622,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr"/>
@@ -16006,11 +15654,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
@@ -16066,11 +15710,7 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="B14" s="11" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr"/>
       <c r="D14" s="11" t="inlineStr"/>
       <c r="E14" s="11" t="inlineStr"/>
@@ -16098,8 +15738,16 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>KATHERIN</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
@@ -16154,16 +15802,12 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
@@ -16190,11 +15834,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -16222,12 +15862,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="10" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr"/>
@@ -16254,9 +15894,9 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>LIZBET</t>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr"/>
@@ -16286,7 +15926,11 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ALDAID</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
@@ -16314,16 +15958,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="11" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr"/>
@@ -16334,16 +15970,8 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LUCERO</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ABIGAILH</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
@@ -16358,18 +15986,26 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BRINDY</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MIRIAN</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr"/>
@@ -16396,19 +16032,11 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
-        </is>
-      </c>
+          <t>ELVIS</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr"/>
+      <c r="D24" s="11" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
@@ -16418,11 +16046,7 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>SAMANTHAG</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr"/>
@@ -16440,14 +16064,10 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
-        </is>
-      </c>
+          <t>VENUS</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr"/>
@@ -16458,8 +16078,16 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>YULISSA</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>PILAR</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
@@ -16486,11 +16114,7 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
+      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr"/>
@@ -16506,11 +16130,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="10" t="inlineStr"/>
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="10" t="inlineStr"/>
@@ -16522,9 +16142,9 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>ADRIAN</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr"/>
@@ -16542,11 +16162,7 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>ELIZABETH</t>
-        </is>
-      </c>
+      <c r="B28" s="11" t="inlineStr"/>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr"/>
@@ -16574,7 +16190,11 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="inlineStr"/>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="10" t="inlineStr"/>
@@ -16586,11 +16206,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
+      <c r="J29" s="10" t="inlineStr"/>
       <c r="K29" s="10" t="inlineStr"/>
       <c r="L29" s="10" t="inlineStr"/>
       <c r="M29" s="10" t="inlineStr"/>
@@ -16636,7 +16252,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr"/>
@@ -16678,11 +16294,7 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>ENZO</t>
-        </is>
-      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr"/>
@@ -16712,7 +16324,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>JORDAN</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr"/>
@@ -16730,11 +16342,7 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>FIORELLA</t>
-        </is>
-      </c>
+      <c r="B34" s="11" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="11" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr"/>
@@ -16746,11 +16354,7 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>YOVANNA</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr"/>
@@ -16768,13 +16372,29 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ERIKAO</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
+          <t>LIZBET</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="10" t="inlineStr">
@@ -16782,11 +16402,7 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
+      <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
@@ -16802,11 +16418,7 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr"/>
@@ -16834,11 +16446,7 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="inlineStr"/>
       <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr"/>
@@ -16850,16 +16458,8 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>EMIR</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>NICOLAS</t>
-        </is>
-      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
       <c r="N37" s="10" t="inlineStr"/>
@@ -16876,7 +16476,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>BELINDA</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr"/>
@@ -16892,12 +16492,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>BRINDY</t>
+          <t>ELVIS</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr"/>
@@ -16916,10 +16516,14 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MAFER</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr"/>
+          <t>FLOR</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr"/>
@@ -16930,9 +16534,9 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>XIOMARA</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>ALDAID</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr"/>
@@ -16950,16 +16554,8 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr"/>
@@ -16972,12 +16568,12 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>ANDRE</t>
+          <t>ESTRELLA</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>LIZ</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr"/>
@@ -16994,11 +16590,7 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="inlineStr"/>
       <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr"/>
@@ -17012,14 +16604,34 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>ESTRELLA</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" s="10" t="inlineStr"/>
-      <c r="O41" s="10" t="inlineStr"/>
+          <t>LEONEL</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>XIOMARA</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
       <c r="P41" s="10" t="inlineStr"/>
       <c r="Q41" s="10" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
@@ -17042,11 +16654,7 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>KEISYS</t>
-        </is>
-      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr"/>
@@ -17074,8 +16682,16 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
       <c r="L43" s="10" t="inlineStr"/>
       <c r="M43" s="10" t="inlineStr"/>
       <c r="N43" s="10" t="inlineStr"/>
@@ -17090,11 +16706,7 @@
           <t>16:15</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="B44" s="11" t="inlineStr"/>
       <c r="C44" s="11" t="inlineStr"/>
       <c r="D44" s="11" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr"/>
@@ -17122,7 +16734,11 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>KIOMI</t>
+        </is>
+      </c>
       <c r="C45" s="10" t="inlineStr"/>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="10" t="inlineStr"/>
@@ -17134,7 +16750,11 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
       <c r="M45" s="10" t="inlineStr"/>
@@ -17178,7 +16798,11 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>GREYS</t>
+        </is>
+      </c>
       <c r="C47" s="10" t="inlineStr"/>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="10" t="inlineStr"/>
@@ -17190,7 +16814,11 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
@@ -17208,7 +16836,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>YASMIN</t>
+          <t>RENZO</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr"/>
@@ -17238,7 +16866,11 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>PIERO</t>
+        </is>
+      </c>
       <c r="C49" s="10" t="inlineStr"/>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr"/>
@@ -17266,7 +16898,11 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
       <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="11" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr"/>
@@ -17294,21 +16930,13 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr"/>
+      <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
@@ -17320,7 +16948,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>KATHERIN</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
@@ -17340,16 +16968,24 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr"/>
-      <c r="E52" s="11" t="inlineStr"/>
+          <t>GIAN</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>AXEL</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SALOME</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>YENNIFER</t>
+        </is>
+      </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
@@ -17358,11 +16994,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr"/>
@@ -17378,18 +17010,26 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="10" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
@@ -17398,16 +17038,12 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>BELINDA</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>LILIA</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>ENRIQUE</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
       <c r="N53" s="10" t="inlineStr"/>
@@ -17434,11 +17070,7 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>MAFER</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr"/>
@@ -17454,26 +17086,10 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>ADRIANA</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>RAUL</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="inlineStr"/>
+      <c r="C55" s="10" t="inlineStr"/>
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
@@ -17482,16 +17098,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>JHOSSEPI</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>MILAGROSI</t>
-        </is>
-      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>ROMINA</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
       <c r="N55" s="10" t="inlineStr"/>
@@ -17506,26 +17118,10 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>CRISTOPHERY</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>JEFFERSON</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>ROSARIOC</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr"/>
+      <c r="D56" s="11" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
       <c r="H56" s="11" t="inlineStr"/>
@@ -17534,16 +17130,12 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>LIZBET</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>NADIAU</t>
-        </is>
-      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>MERLY</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
@@ -17570,7 +17162,11 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="J57" s="10" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
       <c r="K57" s="10" t="inlineStr"/>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr"/>
@@ -17626,11 +17222,7 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>MIRIANM</t>
-        </is>
-      </c>
+      <c r="J59" s="10" t="inlineStr"/>
       <c r="K59" s="10" t="inlineStr"/>
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
@@ -17658,16 +17250,8 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>VENUSR</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>AKEMI</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr"/>
@@ -17694,7 +17278,11 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>VENUS</t>
+        </is>
+      </c>
       <c r="K61" s="10" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
@@ -17752,7 +17340,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>YASMIN</t>
+          <t>KIOMI</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr"/>
@@ -17782,11 +17370,7 @@
           <t>21:15</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>ELIZABETH</t>
-        </is>
-      </c>
+      <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr"/>
       <c r="L64" s="11" t="inlineStr"/>
       <c r="M64" s="11" t="inlineStr"/>
@@ -17814,8 +17398,16 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>GREYS</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>AKEMI</t>
+        </is>
+      </c>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
       <c r="N65" s="10" t="inlineStr"/>
@@ -17844,19 +17436,11 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>ANDYM</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>BRYANR</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>LINDSAYF</t>
-        </is>
-      </c>
+          <t>RENZO</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
       <c r="O66" s="11" t="inlineStr"/>
@@ -17884,17 +17468,17 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>YASSER</t>
+          <t>DAYSI</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>ANDREA</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>FEDERICOZ</t>
+          <t>FLOR</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>PIERO</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr"/>
@@ -17924,14 +17508,10 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>JULISSA</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>MARCO</t>
-        </is>
-      </c>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr"/>
       <c r="L68" s="11" t="inlineStr"/>
       <c r="M68" s="11" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr"/>
@@ -17958,7 +17538,11 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
       <c r="K69" s="10" t="inlineStr"/>
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="inlineStr"/>
@@ -17988,29 +17572,25 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>GIAN</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>FIORELLA</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>SHADIA</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>NORITH</t>
-        </is>
-      </c>
+          <t>YENNIFER</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
       <c r="P70" s="11" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr"/>
@@ -18036,33 +17616,49 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>CRISTOPHERY</t>
+          <t>LIZBET</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>ERIKAO</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>JEFFERSON</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>ROSARIOC</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>VICTORQ</t>
-        </is>
-      </c>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+          <t>ANDRE</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>LOURDES</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>ROSARIO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
